--- a/data-raw/base_viol_mulher.xlsx
+++ b/data-raw/base_viol_mulher.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B2">
@@ -387,17 +387,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B3">
@@ -405,17 +405,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B4">
@@ -423,17 +423,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B5">
@@ -441,17 +441,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D5">
-        <v>926</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B6">
@@ -459,17 +459,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D6">
-        <v>883</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B7">
@@ -477,17 +477,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D7">
-        <v>2991</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B8">
@@ -495,17 +495,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B9">
@@ -513,17 +513,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B10">
@@ -531,17 +531,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D10">
-        <v>22</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B11">
@@ -549,17 +549,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D11">
-        <v>845</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B12">
@@ -567,17 +567,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D12">
-        <v>716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B13">
@@ -585,17 +585,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D13">
-        <v>2662</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B14">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B15">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B16">
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B17">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>1014</v>
+        <v>975</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B18">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>861</v>
+        <v>801</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B19">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>3098</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B20">
@@ -711,17 +711,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D20">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B21">
@@ -729,17 +729,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B22">
@@ -747,17 +747,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D22">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B23">
@@ -765,17 +765,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D23">
-        <v>730</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B24">
@@ -783,17 +783,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D24">
-        <v>736</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B25">
@@ -801,17 +801,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D25">
-        <v>2648</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B26">
@@ -819,17 +819,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>890</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B27">
@@ -837,17 +837,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>854</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B28">
@@ -855,17 +855,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D28">
-        <v>19</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B29">
@@ -873,17 +873,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D29">
-        <v>794</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B30">
@@ -891,17 +891,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D30">
-        <v>737</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B31">
@@ -909,17 +909,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D31">
-        <v>2565</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B32">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B33">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B34">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="D34">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B35">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D35">
-        <v>813</v>
+        <v>771</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B36">
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="D36">
-        <v>712</v>
+        <v>687</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B37">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="D37">
-        <v>2386</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B38">
@@ -1035,17 +1035,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B39">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B40">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D40">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B41">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D41">
-        <v>712</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B42">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D42">
-        <v>774</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B43">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D43">
-        <v>2433</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B44">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B45">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>761</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B46">
@@ -1179,17 +1179,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D46">
-        <v>19</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B47">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D47">
-        <v>715</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B48">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D48">
-        <v>741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B49">
@@ -1233,17 +1233,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D49">
-        <v>2455</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B50">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B51">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B52">
@@ -1297,7 +1297,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B53">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="D53">
-        <v>749</v>
+        <v>707</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B54">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D54">
-        <v>695</v>
+        <v>760</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/1º Semestre</t>
         </is>
       </c>
       <c r="B55">
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="D55">
-        <v>2475</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B56">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B57">
@@ -1377,17 +1377,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B58">
@@ -1395,17 +1395,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D58">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B59">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D59">
-        <v>766</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B60">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D60">
-        <v>821</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B61">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D61">
-        <v>2863</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B62">
@@ -1467,17 +1467,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D62">
-        <v>7</v>
+        <v>889</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B63">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>733</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B64">
@@ -1503,17 +1503,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D64">
-        <v>21</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B65">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D65">
-        <v>750</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B66">
@@ -1539,17 +1539,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D66">
-        <v>741</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B67">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D67">
-        <v>2541</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B68">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="D68">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B69">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B70">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="D70">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B71">
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="D71">
-        <v>774</v>
+        <v>979</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B72">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="D72">
-        <v>724</v>
+        <v>878</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B73">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="D73">
-        <v>2842</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B74">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B75">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B76">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D76">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B77">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D77">
-        <v>996</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B78">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D78">
-        <v>937</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B79">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D79">
-        <v>3155</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B80">
@@ -1791,17 +1791,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>904</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B81">
@@ -1809,17 +1809,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>872</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B82">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D82">
-        <v>15</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B83">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D83">
-        <v>823</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B84">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D84">
-        <v>793</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B85">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D85">
-        <v>2647</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B86">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D86">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B87">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B88">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="D88">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B89">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="D89">
-        <v>1079</v>
+        <v>783</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B90">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="D90">
-        <v>846</v>
+        <v>816</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B91">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="D91">
-        <v>2828</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B92">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D92">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B93">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B94">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D94">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B95">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D95">
-        <v>1052</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B96">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D96">
-        <v>976</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B97">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D97">
-        <v>2909</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B98">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D98">
-        <v>7</v>
+        <v>941</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B99">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>780</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B100">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D100">
-        <v>18</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B101">
@@ -2169,17 +2169,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D101">
-        <v>898</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B102">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D102">
-        <v>923</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B103">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D103">
-        <v>2618</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B104">
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B105">
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B106">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="D106">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B107">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="D107">
-        <v>920</v>
+        <v>952</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B108">
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="D108">
-        <v>687</v>
+        <v>813</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021/2º Semestre</t>
         </is>
       </c>
       <c r="B109">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="D109">
-        <v>2325</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B110">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D110">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B111">
@@ -2349,17 +2349,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B112">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D112">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B113">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D113">
-        <v>930</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B114">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D114">
-        <v>742</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B115">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D115">
-        <v>2531</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B116">
@@ -2439,17 +2439,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D116">
-        <v>6</v>
+        <v>922</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B117">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>836</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B118">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D118">
-        <v>29</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B119">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D119">
-        <v>790</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B120">
@@ -2511,17 +2511,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D120">
-        <v>768</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B121">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D121">
-        <v>2696</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B122">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="D122">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B123">
@@ -2575,7 +2575,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B124">
@@ -2593,7 +2593,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B125">
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="D125">
-        <v>933</v>
+        <v>898</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B126">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="D126">
-        <v>885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B127">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="D127">
-        <v>2779</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B128">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D128">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B129">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B130">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D130">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B131">
@@ -2709,17 +2709,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D131">
-        <v>904</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B132">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D132">
-        <v>886</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B133">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D133">
-        <v>3123</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B134">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D134">
-        <v>9</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B135">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>870</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B136">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D136">
-        <v>19</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B137">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D137">
-        <v>1016</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B138">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D138">
-        <v>828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B139">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D139">
-        <v>2837</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B140">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="D140">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B141">
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B142">
@@ -2911,13 +2911,13 @@
         </is>
       </c>
       <c r="D142">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B143">
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="D143">
-        <v>1062</v>
+        <v>843</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B144">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="D144">
-        <v>842</v>
+        <v>718</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B145">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="D145">
-        <v>2946</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B146">
@@ -2979,17 +2979,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D146">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B147">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B148">
@@ -3015,17 +3015,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D148">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B149">
@@ -3033,17 +3033,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D149">
-        <v>977</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B150">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D150">
-        <v>903</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B151">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D151">
-        <v>3062</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B152">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D152">
-        <v>8</v>
+        <v>819</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B153">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D153">
-        <v>6</v>
+        <v>730</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B154">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D154">
-        <v>20</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B155">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D155">
-        <v>1034</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B156">
@@ -3159,17 +3159,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D156">
-        <v>872</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B157">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D157">
-        <v>2707</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B158">
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="D158">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B159">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="D159">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B160">
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="D160">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B161">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="D161">
-        <v>926</v>
+        <v>670</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B162">
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="D162">
-        <v>730</v>
+        <v>638</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/1º Semestre</t>
         </is>
       </c>
       <c r="B163">
@@ -3289,13 +3289,13 @@
         </is>
       </c>
       <c r="D163">
-        <v>2673</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B164">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B165">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D165">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B166">
@@ -3339,17 +3339,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D166">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B167">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D167">
-        <v>594</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B168">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D168">
-        <v>634</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B169">
@@ -3393,17 +3393,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D169">
-        <v>2016</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B170">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D170">
-        <v>6</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B171">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D171">
-        <v>6</v>
+        <v>698</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B172">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D172">
-        <v>16</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B173">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D173">
-        <v>599</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B174">
@@ -3483,17 +3483,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D174">
-        <v>540</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B175">
@@ -3501,17 +3501,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D175">
-        <v>2098</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B176">
@@ -3523,13 +3523,13 @@
         </is>
       </c>
       <c r="D176">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B177">
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="D177">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B178">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="D178">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B179">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="D179">
-        <v>692</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B180">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="D180">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B181">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="D181">
-        <v>2347</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B182">
@@ -3627,17 +3627,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D182">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B183">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D183">
@@ -3655,7 +3655,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B184">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D184">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B185">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D185">
-        <v>624</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B186">
@@ -3699,17 +3699,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D186">
-        <v>756</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B187">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D187">
-        <v>2446</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B188">
@@ -3735,17 +3735,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D188">
-        <v>4</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B189">
@@ -3753,17 +3753,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>699</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B190">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D190">
-        <v>21</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B191">
@@ -3789,17 +3789,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D191">
-        <v>698</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B192">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D192">
-        <v>663</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B193">
@@ -3825,17 +3825,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D193">
-        <v>2453</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B194">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="D194">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B195">
@@ -3865,13 +3865,13 @@
         </is>
       </c>
       <c r="D195">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B196">
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="D196">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B197">
@@ -3901,13 +3901,13 @@
         </is>
       </c>
       <c r="D197">
-        <v>718</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B198">
@@ -3919,13 +3919,13 @@
         </is>
       </c>
       <c r="D198">
-        <v>844</v>
+        <v>798</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B199">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="D199">
-        <v>2747</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B200">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B201">
@@ -3969,17 +3969,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D201">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B202">
@@ -3987,17 +3987,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D202">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B203">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D203">
-        <v>930</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B204">
@@ -4023,17 +4023,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D204">
-        <v>785</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B205">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D205">
-        <v>2919</v>
+        <v>27</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B206">
@@ -4059,17 +4059,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D206">
-        <v>9</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B207">
@@ -4077,17 +4077,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D207">
-        <v>9</v>
+        <v>676</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B208">
@@ -4095,17 +4095,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D208">
-        <v>24</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B209">
@@ -4113,17 +4113,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D209">
-        <v>862</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B210">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D210">
-        <v>824</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B211">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D211">
-        <v>2981</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B212">
@@ -4177,7 +4177,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B213">
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="D213">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B214">
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="D214">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B215">
@@ -4225,13 +4225,13 @@
         </is>
       </c>
       <c r="D215">
-        <v>918</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B216">
@@ -4243,13 +4243,13 @@
         </is>
       </c>
       <c r="D216">
-        <v>802</v>
+        <v>741</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022/2º Semestre</t>
         </is>
       </c>
       <c r="B217">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="D217">
-        <v>2826</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B218">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B219">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D219">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B220">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D220">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B221">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D221">
-        <v>994</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B222">
@@ -4347,17 +4347,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D222">
-        <v>846</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B223">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D223">
-        <v>3130</v>
+        <v>25</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B224">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D224">
-        <v>5</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B225">
@@ -4401,17 +4401,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D225">
-        <v>3</v>
+        <v>804</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B226">
@@ -4419,17 +4419,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D226">
-        <v>24</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B227">
@@ -4437,17 +4437,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D227">
-        <v>975</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B228">
@@ -4455,17 +4455,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D228">
-        <v>801</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B229">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D229">
-        <v>2590</v>
+        <v>18</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B230">
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="D230">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B231">
@@ -4513,13 +4513,13 @@
         </is>
       </c>
       <c r="D231">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B232">
@@ -4537,7 +4537,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B233">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="D233">
-        <v>890</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B234">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="D234">
-        <v>854</v>
+        <v>712</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B235">
@@ -4585,13 +4585,13 @@
         </is>
       </c>
       <c r="D235">
-        <v>2907</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B236">
@@ -4599,17 +4599,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D236">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B237">
@@ -4617,17 +4617,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D237">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B238">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D238">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B239">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D239">
-        <v>771</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B240">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D240">
-        <v>687</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B241">
@@ -4689,17 +4689,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D241">
-        <v>2398</v>
+        <v>26</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B242">
@@ -4707,17 +4707,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D242">
-        <v>7</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B243">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>796</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B244">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D244">
-        <v>29</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B245">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D245">
-        <v>695</v>
+        <v>7</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B246">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D246">
-        <v>761</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B247">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D247">
-        <v>2358</v>
+        <v>9</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B248">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D248">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B249">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B250">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="D250">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B251">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="D251">
-        <v>707</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B252">
@@ -4891,13 +4891,13 @@
         </is>
       </c>
       <c r="D252">
-        <v>760</v>
+        <v>640</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B253">
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="D253">
-        <v>2242</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B254">
@@ -4923,17 +4923,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D254">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B255">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D255">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B256">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D256">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B257">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D257">
-        <v>889</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B258">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D258">
-        <v>733</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B259">
@@ -5013,17 +5013,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D259">
-        <v>2319</v>
+        <v>22</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B260">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D260">
-        <v>5</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B261">
@@ -5049,17 +5049,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D261">
-        <v>5</v>
+        <v>728</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B262">
@@ -5067,17 +5067,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D262">
-        <v>20</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B263">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D263">
-        <v>979</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B264">
@@ -5103,17 +5103,17 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D264">
-        <v>878</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B265">
@@ -5121,17 +5121,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D265">
-        <v>2701</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B266">
@@ -5143,13 +5143,13 @@
         </is>
       </c>
       <c r="D266">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B267">
@@ -5161,13 +5161,13 @@
         </is>
       </c>
       <c r="D267">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B268">
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="D268">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B269">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="D269">
-        <v>904</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B270">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D270">
-        <v>872</v>
+        <v>655</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/1º Semestre</t>
         </is>
       </c>
       <c r="B271">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="D271">
-        <v>2787</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B272">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D272">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B273">
@@ -5265,17 +5265,17 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D273">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B274">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>FEMINICÍDIO</t>
         </is>
       </c>
       <c r="D274">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B275">
@@ -5301,17 +5301,17 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D275">
-        <v>783</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B276">
@@ -5319,17 +5319,17 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D276">
-        <v>816</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B277">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
+          <t>HOMICÍDIO DOLOSO - TOTAL</t>
         </is>
       </c>
       <c r="D277">
-        <v>2682</v>
+        <v>14</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B278">
@@ -5355,17 +5355,17 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D278">
-        <v>5</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B279">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D279">
-        <v>1</v>
+        <v>671</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023/2º Semestre</t>
         </is>
       </c>
       <c r="B280">
@@ -5391,1469 +5391,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
+          <t>LESÃO CORPORAL DOLOSA</t>
         </is>
       </c>
       <c r="D280">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B281">
-        <v>10</v>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D281">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B282">
-        <v>20</v>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D282">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B283">
-        <v>30</v>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D283">
-        <v>2831</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B284">
-        <v>10</v>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D284">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B285">
-        <v>20</v>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D285">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B286">
-        <v>30</v>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D286">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B287">
-        <v>10</v>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D287">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B288">
-        <v>20</v>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D288">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B289">
-        <v>30</v>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D289">
-        <v>2929</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B290">
-        <v>10</v>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D290">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B291">
-        <v>20</v>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D291">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B292">
-        <v>30</v>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D292">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B293">
-        <v>10</v>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D293">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B294">
-        <v>20</v>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D294">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B295">
-        <v>30</v>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D295">
-        <v>2710</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B296">
-        <v>10</v>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D296">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B297">
-        <v>20</v>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D297">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B298">
-        <v>30</v>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D298">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B299">
-        <v>10</v>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D299">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B300">
-        <v>20</v>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D300">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B301">
-        <v>30</v>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D301">
-        <v>2664</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B302">
-        <v>10</v>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D302">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B303">
-        <v>20</v>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D303">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B304">
-        <v>30</v>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D304">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B305">
-        <v>10</v>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D305">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B306">
-        <v>20</v>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D306">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B307">
-        <v>30</v>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D307">
-        <v>3197</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B308">
-        <v>10</v>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D308">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B309">
-        <v>20</v>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D309">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B310">
-        <v>30</v>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D310">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B311">
-        <v>10</v>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D311">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B312">
-        <v>20</v>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D312">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B313">
-        <v>30</v>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D313">
-        <v>2617</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B314">
-        <v>10</v>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D314">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B315">
-        <v>20</v>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D315">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B316">
-        <v>30</v>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D316">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B317">
-        <v>10</v>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D317">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B318">
-        <v>20</v>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D318">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B319">
-        <v>30</v>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D319">
-        <v>2341</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B320">
-        <v>10</v>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D320">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B321">
-        <v>20</v>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D321">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B322">
-        <v>30</v>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D322">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B323">
-        <v>10</v>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D323">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B324">
-        <v>20</v>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D324">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B325">
-        <v>30</v>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D325">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B326">
-        <v>10</v>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D326">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B327">
-        <v>20</v>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D327">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B328">
-        <v>30</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D328">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B329">
-        <v>10</v>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D329">
-        <v>1456</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B330">
-        <v>20</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D330">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B331">
-        <v>30</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D331">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B332">
-        <v>10</v>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D332">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B333">
-        <v>20</v>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D333">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B334">
-        <v>30</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D334">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B335">
-        <v>10</v>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D335">
-        <v>1508</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B336">
-        <v>20</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D336">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B337">
-        <v>30</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D337">
-        <v>3514</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B338">
-        <v>10</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D338">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B339">
-        <v>20</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D339">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B340">
-        <v>30</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D340">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B341">
-        <v>10</v>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D341">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B342">
-        <v>20</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D342">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B343">
-        <v>30</v>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D343">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B344">
-        <v>10</v>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D344">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B345">
-        <v>20</v>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D345">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B346">
-        <v>30</v>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D346">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B347">
-        <v>10</v>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D347">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B348">
-        <v>20</v>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D348">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B349">
-        <v>30</v>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D349">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B350">
-        <v>10</v>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D350">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B351">
-        <v>20</v>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D351">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B352">
-        <v>30</v>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D352">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B353">
-        <v>10</v>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D353">
-        <v>1562</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B354">
-        <v>20</v>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D354">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B355">
-        <v>30</v>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D355">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B356">
-        <v>10</v>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D356">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B357">
-        <v>20</v>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D357">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B358">
-        <v>30</v>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>HOMICÍDIO DOLOSO - TOTAL</t>
-        </is>
-      </c>
-      <c r="D358">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B359">
-        <v>10</v>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D359">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B360">
-        <v>20</v>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D360">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B361">
-        <v>30</v>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>LESÃO CORPORAL DOLOSA</t>
-        </is>
-      </c>
-      <c r="D361">
-        <v>2325</v>
+        <v>2164</v>
       </c>
     </row>
   </sheetData>
